--- a/data/trans_camb/P34A_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P34A_R-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-24,34; -12,83</t>
+          <t>-25,02; -13,42</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-15,7; -3,34</t>
+          <t>-16,13; -3,78</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-13,9; -2,06</t>
+          <t>-13,79; -1,54</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-23,1; -8,28</t>
+          <t>-22,65; -7,97</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-16,47; -1,52</t>
+          <t>-16,11; -1,53</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-20,78; -7,14</t>
+          <t>-20,47; -7,33</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-22,08; -12,91</t>
+          <t>-22,68; -12,98</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-13,11; -4,2</t>
+          <t>-14,1; -4,59</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-15,15; -6,17</t>
+          <t>-14,72; -5,74</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-64,87; -40,46</t>
+          <t>-65,77; -41,16</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-41,9; -10,76</t>
+          <t>-42,13; -11,63</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-36,64; -6,0</t>
+          <t>-36,5; -4,65</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-56,93; -24,65</t>
+          <t>-56,1; -23,38</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-39,85; -3,65</t>
+          <t>-38,75; -4,65</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-50,03; -21,92</t>
+          <t>-50,0; -22,52</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-58,1; -38,76</t>
+          <t>-59,11; -38,24</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-34,76; -12,49</t>
+          <t>-36,9; -13,74</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-39,1; -18,46</t>
+          <t>-38,16; -17,32</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-18,57; -5,66</t>
+          <t>-17,84; -5,86</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10,93; 2,29</t>
+          <t>-10,28; 2,62</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-10,95; 1,4</t>
+          <t>-10,85; 1,44</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-24,31; -9,51</t>
+          <t>-24,74; -10,45</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-18,14; -3,45</t>
+          <t>-17,7; -3,31</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-16,62; -3,27</t>
+          <t>-16,37; -3,49</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-19,87; -10,25</t>
+          <t>-20,06; -10,34</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-12,81; -2,43</t>
+          <t>-12,4; -2,57</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-12,02; -2,85</t>
+          <t>-11,84; -2,83</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-55,75; -22,66</t>
+          <t>-53,92; -20,89</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-32,81; 8,63</t>
+          <t>-30,4; 10,13</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-32,4; 5,68</t>
+          <t>-32,76; 5,42</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-52,95; -24,95</t>
+          <t>-52,19; -24,75</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-39,61; -8,75</t>
+          <t>-38,17; -7,97</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-35,65; -8,55</t>
+          <t>-35,4; -9,28</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-50,79; -29,81</t>
+          <t>-51,64; -30,59</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-32,68; -7,28</t>
+          <t>-31,89; -7,47</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-31,0; -8,72</t>
+          <t>-30,92; -9,09</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-26,58; -15,38</t>
+          <t>-26,68; -15,09</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-15,68; -3,48</t>
+          <t>-15,68; -3,55</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-39,3; -7,05</t>
+          <t>-39,11; -6,89</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-22,49; -2,55</t>
+          <t>-20,78; -2,16</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-16,0; 6,66</t>
+          <t>-16,61; 6,01</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-15,85; 4,68</t>
+          <t>-16,06; 4,22</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-22,95; -12,97</t>
+          <t>-22,91; -13,18</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-13,61; -2,59</t>
+          <t>-13,69; -2,51</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-34,59; -6,45</t>
+          <t>-34,91; -6,54</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-54,16; -35,02</t>
+          <t>-53,84; -34,63</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-31,81; -7,84</t>
+          <t>-31,46; -7,98</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-80,79; -15,2</t>
+          <t>-79,58; -14,96</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-42,42; -6,83</t>
+          <t>-40,89; -4,76</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-31,3; 16,0</t>
+          <t>-31,12; 14,62</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-29,4; 12,82</t>
+          <t>-30,44; 11,04</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-46,95; -29,38</t>
+          <t>-47,26; -30,05</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-28,39; -6,44</t>
+          <t>-27,99; -5,94</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-73,84; -14,16</t>
+          <t>-77,52; -14,43</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-25,77; -17,88</t>
+          <t>-25,27; -17,9</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-12,34; -4,34</t>
+          <t>-12,65; -4,4</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-12,74; -4,37</t>
+          <t>-12,76; -4,42</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-21,95; -11,62</t>
+          <t>-21,7; -11,18</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-9,45; 0,52</t>
+          <t>-9,76; 0,81</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-31,78; -6,26</t>
+          <t>-32,48; -6,04</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-22,85; -16,45</t>
+          <t>-22,7; -16,51</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-10,13; -3,81</t>
+          <t>-10,09; -3,65</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-23,86; -7,04</t>
+          <t>-23,36; -7,21</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-52,55; -39,27</t>
+          <t>-52,16; -39,51</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-25,48; -9,75</t>
+          <t>-25,64; -9,73</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-26,09; -9,74</t>
+          <t>-26,29; -9,83</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-44,1; -26,45</t>
+          <t>-43,4; -25,71</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-19,53; 0,85</t>
+          <t>-19,4; 1,82</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-64,8; -13,66</t>
+          <t>-66,15; -13,09</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-46,65; -35,99</t>
+          <t>-46,63; -35,94</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-20,57; -8,42</t>
+          <t>-20,91; -8,11</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-49,61; -15,18</t>
+          <t>-50,87; -15,51</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-29,46; -15,76</t>
+          <t>-29,9; -15,89</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-17,64; -3,36</t>
+          <t>-16,65; -2,97</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-15,3; -0,8</t>
+          <t>-15,04; -0,7</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-22,75; -11,57</t>
+          <t>-22,34; -11,46</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-11,62; -0,47</t>
+          <t>-12,13; -0,57</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-19,82; -1,29</t>
+          <t>-20,22; -0,34</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-23,91; -15,05</t>
+          <t>-23,95; -15,01</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-12,68; -3,74</t>
+          <t>-12,49; -3,5</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-15,69; -2,77</t>
+          <t>-15,31; -2,41</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-54,42; -33,81</t>
+          <t>-54,15; -33,56</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-31,78; -6,69</t>
+          <t>-30,38; -6,47</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-27,86; -1,7</t>
+          <t>-27,85; -1,57</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-40,15; -22,64</t>
+          <t>-39,21; -21,89</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-20,61; -0,93</t>
+          <t>-21,15; -1,17</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-35,64; -2,44</t>
+          <t>-36,57; -0,88</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-43,49; -29,94</t>
+          <t>-43,34; -30,09</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-22,91; -7,38</t>
+          <t>-22,51; -7,05</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-29,04; -5,63</t>
+          <t>-28,35; -4,8</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-13,55; -0,91</t>
+          <t>-13,59; -1,26</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-7,88; 5,21</t>
+          <t>-7,21; 5,53</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-13,54; 5,69</t>
+          <t>-13,44; 6,18</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-18,35; -10,31</t>
+          <t>-18,7; -11,06</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 6,61</t>
+          <t>-1,49; 6,89</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 8,37</t>
+          <t>-0,1; 8,42</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-16,67; -9,61</t>
+          <t>-16,55; -9,73</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-2,41; 5,13</t>
+          <t>-2,81; 4,92</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-4,09; 4,78</t>
+          <t>-4,05; 4,81</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-61,25; -5,46</t>
+          <t>-60,32; -8,01</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-35,57; 33,85</t>
+          <t>-33,73; 33,41</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-66,76; 35,45</t>
+          <t>-65,46; 43,08</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-39,48; -23,85</t>
+          <t>-39,68; -25,53</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-3,66; 15,47</t>
+          <t>-3,2; 15,77</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 19,38</t>
+          <t>-0,4; 19,49</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-40,39; -25,06</t>
+          <t>-40,04; -25,33</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-5,7; 13,46</t>
+          <t>-6,63; 12,75</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-9,64; 12,48</t>
+          <t>-9,74; 12,33</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-20,86; -16,26</t>
+          <t>-20,92; -16,51</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-9,63; -4,88</t>
+          <t>-9,59; -4,77</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-17,17; -6,81</t>
+          <t>-17,64; -6,73</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-17,31; -12,53</t>
+          <t>-17,41; -12,84</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-5,86; -0,95</t>
+          <t>-5,87; -0,92</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-14,64; -4,25</t>
+          <t>-14,89; -4,21</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-18,52; -15,2</t>
+          <t>-18,39; -15,24</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-6,99; -3,58</t>
+          <t>-6,99; -3,56</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-13,75; -6,28</t>
+          <t>-12,98; -6,16</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-49,63; -40,87</t>
+          <t>-49,31; -41,11</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-22,8; -12,31</t>
+          <t>-22,97; -12,1</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-41,81; -16,85</t>
+          <t>-41,68; -16,68</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-36,74; -28,07</t>
+          <t>-36,95; -28,44</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-12,42; -2,15</t>
+          <t>-12,46; -2,16</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-32,0; -9,7</t>
+          <t>-31,96; -9,23</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-41,73; -35,62</t>
+          <t>-41,57; -35,73</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-15,71; -8,41</t>
+          <t>-15,72; -8,45</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-31,26; -14,58</t>
+          <t>-29,49; -14,23</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P34A_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P34A_R-Clase-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-7,71</t>
+          <t>-7,93</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-13,71</t>
+          <t>-13,49</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-10,36</t>
+          <t>-10,38</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-25,02; -13,42</t>
+          <t>-24,8; -13,43</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-16,13; -3,78</t>
+          <t>-15,27; -3,24</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-13,79; -1,54</t>
+          <t>-13,91; -1,96</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-22,65; -7,97</t>
+          <t>-22,53; -7,87</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-16,11; -1,53</t>
+          <t>-15,73; -0,43</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-20,47; -7,33</t>
+          <t>-19,98; -6,85</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-22,68; -12,98</t>
+          <t>-22,03; -13,3</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-14,1; -4,59</t>
+          <t>-14,01; -4,49</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-14,72; -5,74</t>
+          <t>-14,95; -6,49</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-22,15%</t>
+          <t>-22,79%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-37,15%</t>
+          <t>-36,53%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-29,09%</t>
+          <t>-29,13%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-65,77; -41,16</t>
+          <t>-65,89; -42,4</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-42,13; -11,63</t>
+          <t>-40,66; -8,92</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-36,5; -4,65</t>
+          <t>-36,79; -6,2</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-56,1; -23,38</t>
+          <t>-55,98; -23,39</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-38,75; -4,65</t>
+          <t>-39,14; -1,3</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-50,0; -22,52</t>
+          <t>-48,63; -20,94</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-59,11; -38,24</t>
+          <t>-58,18; -39,34</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-36,9; -13,74</t>
+          <t>-36,67; -13,36</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-38,16; -17,32</t>
+          <t>-38,78; -19,1</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-4,46</t>
+          <t>-4,45</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-9,92</t>
+          <t>-9,82</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-7,52</t>
+          <t>-7,4</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-17,84; -5,86</t>
+          <t>-17,88; -5,64</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10,28; 2,62</t>
+          <t>-10,36; 3,04</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-10,85; 1,44</t>
+          <t>-10,66; 1,59</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-24,74; -10,45</t>
+          <t>-23,76; -10,01</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-17,7; -3,31</t>
+          <t>-17,56; -3,03</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-16,37; -3,49</t>
+          <t>-16,58; -3,27</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-20,06; -10,34</t>
+          <t>-20,06; -10,19</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-12,4; -2,57</t>
+          <t>-12,58; -2,6</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-11,84; -2,83</t>
+          <t>-12,32; -2,72</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-14,87%</t>
+          <t>-14,82%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-23,2%</t>
+          <t>-22,96%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-20,65%</t>
+          <t>-20,32%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-53,92; -20,89</t>
+          <t>-53,73; -21,35</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-30,4; 10,13</t>
+          <t>-31,25; 11,67</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-32,76; 5,42</t>
+          <t>-32,04; 6,27</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-52,19; -24,75</t>
+          <t>-51,82; -25,34</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-38,17; -7,97</t>
+          <t>-39,18; -8,35</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-35,4; -9,28</t>
+          <t>-35,17; -8,18</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-51,64; -30,59</t>
+          <t>-50,96; -29,78</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-31,89; -7,47</t>
+          <t>-31,85; -7,66</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-30,92; -9,09</t>
+          <t>-31,45; -8,23</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-22,57</t>
+          <t>-9,29</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-6,08</t>
+          <t>-4,93</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-19,28</t>
+          <t>-8,03</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-26,68; -15,09</t>
+          <t>-26,97; -15,56</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-15,68; -3,55</t>
+          <t>-15,96; -3,53</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-39,11; -6,89</t>
+          <t>-15,26; -2,47</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-20,78; -2,16</t>
+          <t>-21,01; -1,06</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-16,61; 6,01</t>
+          <t>-15,63; 7,09</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-16,06; 4,22</t>
+          <t>-14,66; 5,07</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-22,91; -13,18</t>
+          <t>-22,81; -13,05</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-13,69; -2,51</t>
+          <t>-13,89; -2,97</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-34,91; -6,54</t>
+          <t>-13,31; -2,51</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-48,7%</t>
+          <t>-20,03%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-13,04%</t>
+          <t>-10,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-41,55%</t>
+          <t>-17,31%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-53,84; -34,63</t>
+          <t>-54,38; -35,59</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-31,46; -7,98</t>
+          <t>-31,99; -7,75</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-79,58; -14,96</t>
+          <t>-30,99; -5,68</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-40,89; -4,76</t>
+          <t>-40,02; -2,89</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-31,12; 14,62</t>
+          <t>-30,0; 17,08</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-30,44; 11,04</t>
+          <t>-28,12; 12,27</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-47,26; -30,05</t>
+          <t>-46,37; -30,16</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-27,99; -5,94</t>
+          <t>-28,02; -6,72</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-77,52; -14,43</t>
+          <t>-27,28; -5,8</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-8,7</t>
+          <t>-9,09</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-15,97</t>
+          <t>-6,87</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-12,2</t>
+          <t>-8,11</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-25,27; -17,9</t>
+          <t>-25,41; -17,68</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-12,65; -4,4</t>
+          <t>-12,68; -4,22</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-12,76; -4,42</t>
+          <t>-13,33; -5,09</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-21,7; -11,18</t>
+          <t>-21,96; -12,14</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-9,76; 0,81</t>
+          <t>-10,06; 0,22</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-32,48; -6,04</t>
+          <t>-12,11; -2,28</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-22,7; -16,51</t>
+          <t>-22,85; -16,42</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-10,09; -3,65</t>
+          <t>-9,97; -3,63</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-23,36; -7,21</t>
+          <t>-11,14; -4,9</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-18,48%</t>
+          <t>-19,33%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-33,72%</t>
+          <t>-14,51%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-25,87%</t>
+          <t>-17,2%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-52,16; -39,51</t>
+          <t>-52,46; -39,43</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-25,64; -9,73</t>
+          <t>-25,62; -9,32</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-26,29; -9,83</t>
+          <t>-27,3; -10,98</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-43,4; -25,71</t>
+          <t>-43,74; -26,63</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-19,4; 1,82</t>
+          <t>-19,95; 0,63</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-66,15; -13,09</t>
+          <t>-24,2; -5,4</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-46,63; -35,94</t>
+          <t>-46,72; -36,13</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-20,91; -8,11</t>
+          <t>-20,45; -8,15</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-50,87; -15,51</t>
+          <t>-22,98; -10,79</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-7,78</t>
+          <t>-6,66</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-8,78</t>
+          <t>-8,29</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-8,35</t>
+          <t>-7,7</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-29,9; -15,89</t>
+          <t>-29,05; -15,72</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-16,65; -2,97</t>
+          <t>-16,85; -3,84</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-15,04; -0,7</t>
+          <t>-13,85; 0,32</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-22,34; -11,46</t>
+          <t>-22,61; -11,47</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-12,13; -0,57</t>
+          <t>-11,27; 0,34</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-20,22; -0,34</t>
+          <t>-13,6; -3,29</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-23,95; -15,01</t>
+          <t>-23,72; -14,95</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-12,49; -3,5</t>
+          <t>-12,53; -3,37</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-15,31; -2,41</t>
+          <t>-11,61; -3,36</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-15,3%</t>
+          <t>-13,1%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-16,25%</t>
+          <t>-15,34%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-15,82%</t>
+          <t>-14,59%</t>
         </is>
       </c>
     </row>
@@ -1647,54 +1647,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-54,15; -33,56</t>
+          <t>-53,04; -33,11</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-30,38; -6,47</t>
+          <t>-30,64; -8,32</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-27,85; -1,57</t>
+          <t>-25,2; 1,37</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-39,21; -21,89</t>
+          <t>-40,33; -22,63</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-21,15; -1,17</t>
+          <t>-19,92; 0,69</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-36,57; -0,88</t>
+          <t>-23,61; -6,57</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-43,34; -30,09</t>
+          <t>-42,93; -29,48</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-22,51; -7,05</t>
+          <t>-22,46; -6,94</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-28,35; -4,8</t>
+          <t>-21,2; -6,71</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-5,61</t>
+          <t>-6,89</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,25</t>
+          <t>3,82</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0,68</t>
+          <t>0,81</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-13,59; -1,26</t>
+          <t>-13,29; -1,28</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-7,21; 5,53</t>
+          <t>-7,83; 4,81</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-13,44; 6,18</t>
+          <t>-14,04; 4,5</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-18,7; -11,06</t>
+          <t>-18,43; -10,89</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 6,89</t>
+          <t>-1,32; 7,16</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 8,42</t>
+          <t>-0,74; 7,8</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-16,55; -9,73</t>
+          <t>-16,8; -9,63</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 4,92</t>
+          <t>-2,36; 5,23</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-4,05; 4,81</t>
+          <t>-3,19; 5,02</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-29,54%</t>
+          <t>-36,26%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>2,04%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-60,32; -8,01</t>
+          <t>-59,68; -6,39</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-33,73; 33,41</t>
+          <t>-35,34; 31,52</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-65,46; 43,08</t>
+          <t>-67,23; 28,42</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-39,68; -25,53</t>
+          <t>-39,78; -25,26</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 15,77</t>
+          <t>-2,85; 16,26</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 19,49</t>
+          <t>-1,63; 17,96</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-40,04; -25,33</t>
+          <t>-39,85; -24,73</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-6,63; 12,75</t>
+          <t>-5,56; 13,8</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-9,74; 12,33</t>
+          <t>-7,85; 13,02</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-10,12</t>
+          <t>-7,5</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-8,13</t>
+          <t>-5,61</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-9,06</t>
+          <t>-6,5</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-20,92; -16,51</t>
+          <t>-20,89; -16,3</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-9,59; -4,77</t>
+          <t>-9,51; -4,62</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-17,64; -6,73</t>
+          <t>-9,84; -5,14</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-17,41; -12,84</t>
+          <t>-17,43; -12,82</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-5,87; -0,92</t>
+          <t>-5,9; -0,96</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-14,89; -4,21</t>
+          <t>-7,97; -3,42</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-18,39; -15,24</t>
+          <t>-18,33; -15,07</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-6,99; -3,56</t>
+          <t>-6,97; -3,55</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-12,98; -6,16</t>
+          <t>-8,28; -4,91</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-24,64%</t>
+          <t>-18,27%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-17,63%</t>
+          <t>-12,17%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-20,76%</t>
+          <t>-14,89%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-49,31; -41,11</t>
+          <t>-49,42; -40,84</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-22,97; -12,1</t>
+          <t>-22,64; -11,89</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-41,68; -16,68</t>
+          <t>-23,33; -12,92</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-36,95; -28,44</t>
+          <t>-37,03; -28,36</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-12,46; -2,16</t>
+          <t>-12,38; -2,12</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-31,96; -9,23</t>
+          <t>-16,64; -7,71</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-41,57; -35,73</t>
+          <t>-41,47; -35,53</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-15,72; -8,45</t>
+          <t>-15,71; -8,3</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-29,49; -14,23</t>
+          <t>-18,65; -11,52</t>
         </is>
       </c>
     </row>
